--- a/data/trans_bre/P2A_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,38; 20,5</t>
+          <t>8,8; 20,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,22; 17,03</t>
+          <t>4,09; 17,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 10,76</t>
+          <t>-2,33; 11,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 9,37</t>
+          <t>-11,49; 10,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,62; 94,67</t>
+          <t>31,3; 93,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,89; 55,86</t>
+          <t>11,17; 56,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 36,09</t>
+          <t>-6,56; 38,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-33,96; 43,0</t>
+          <t>-32,44; 48,38</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,43; 18,63</t>
+          <t>8,88; 20,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 14,18</t>
+          <t>3,8; 14,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,3; 17,35</t>
+          <t>6,37; 17,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 3,16</t>
+          <t>-15,15; 3,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,61; 64,41</t>
+          <t>26,54; 70,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,33; 36,66</t>
+          <t>8,81; 37,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,45; 62,7</t>
+          <t>19,04; 63,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,37; 11,63</t>
+          <t>-46,81; 12,92</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,51; 24,3</t>
+          <t>13,41; 24,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,69; 20,18</t>
+          <t>9,59; 20,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,44; 19,01</t>
+          <t>8,37; 19,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 10,24</t>
+          <t>-4,35; 9,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,13; 71,93</t>
+          <t>34,52; 71,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,81; 50,93</t>
+          <t>20,64; 52,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,33; 56,58</t>
+          <t>20,61; 57,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 44,84</t>
+          <t>-13,97; 43,42</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,54; 21,62</t>
+          <t>9,8; 21,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,68; 26,68</t>
+          <t>15,45; 26,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 12,55</t>
+          <t>1,46; 12,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 32,03</t>
+          <t>1,35; 31,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,58; 45,58</t>
+          <t>17,91; 46,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,21; 55,82</t>
+          <t>27,86; 54,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 24,26</t>
+          <t>2,62; 24,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 290,0</t>
+          <t>3,27; 215,3</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 9,03</t>
+          <t>-2,22; 9,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,1; 16,34</t>
+          <t>5,52; 15,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,12; 22,31</t>
+          <t>9,59; 21,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 7,2</t>
+          <t>-3,03; 7,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 12,12</t>
+          <t>-2,71; 12,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,27; 21,83</t>
+          <t>6,86; 20,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,43; 35,46</t>
+          <t>13,69; 34,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 14,42</t>
+          <t>-5,43; 13,91</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,46; 17,4</t>
+          <t>7,22; 17,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 4,02</t>
+          <t>-3,19; 4,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 6,89</t>
+          <t>-2,12; 6,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,26; 37,61</t>
+          <t>9,34; 37,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,58; 22,6</t>
+          <t>8,64; 23,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 4,37</t>
+          <t>-3,3; 4,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 8,07</t>
+          <t>-2,3; 8,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,85; 74,63</t>
+          <t>16,58; 73,89</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 7,59</t>
+          <t>-0,91; 7,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 5,63</t>
+          <t>-0,81; 5,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 7,02</t>
+          <t>0,05; 6,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 9,43</t>
+          <t>-1,0; 9,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 8,58</t>
+          <t>-0,95; 8,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 6,14</t>
+          <t>-0,83; 5,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,03; 7,74</t>
+          <t>0,05; 7,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 13,8</t>
+          <t>-1,33; 13,18</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,35; 18,09</t>
+          <t>13,46; 18,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,25; 15,8</t>
+          <t>11,37; 16,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,14; 13,72</t>
+          <t>9,32; 14,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,84; 21,15</t>
+          <t>3,8; 22,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,26; 38,54</t>
+          <t>27,03; 38,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,91; 29,0</t>
+          <t>19,95; 29,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,13; 26,82</t>
+          <t>17,34; 27,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,4; 65,91</t>
+          <t>9,46; 65,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,62</t>
+          <t>4,46</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-2,17%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,8; 20,66</t>
+          <t>9,03; 20,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 17,09</t>
+          <t>4,18; 16,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 11,23</t>
+          <t>-2,51; 10,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 10,3</t>
+          <t>-5,1; 14,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,3; 93,09</t>
+          <t>33,34; 96,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,17; 56,66</t>
+          <t>11,76; 56,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 38,69</t>
+          <t>-7,0; 37,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-32,44; 48,38</t>
+          <t>-18,05; 76,75</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,34</t>
+          <t>-0,43</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-15,17%</t>
+          <t>-1,58%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,88; 20,16</t>
+          <t>8,3; 19,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 14,26</t>
+          <t>3,5; 14,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,37; 17,49</t>
+          <t>6,38; 17,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 3,49</t>
+          <t>-7,43; 5,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,54; 70,2</t>
+          <t>25,36; 70,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,81; 37,23</t>
+          <t>7,93; 37,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,04; 63,86</t>
+          <t>18,71; 63,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,81; 12,92</t>
+          <t>-23,81; 27,06</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,46</t>
+          <t>7,4</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,41; 24,09</t>
+          <t>13,48; 24,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,59; 20,77</t>
+          <t>9,34; 19,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,37; 19,28</t>
+          <t>8,64; 19,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 9,69</t>
+          <t>2,49; 12,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,52; 71,27</t>
+          <t>34,04; 71,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,64; 52,28</t>
+          <t>20,33; 49,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,61; 57,17</t>
+          <t>21,69; 56,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 43,42</t>
+          <t>9,03; 56,2</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,61</t>
+          <t>4,89</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,8; 21,84</t>
+          <t>9,12; 21,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,45; 26,52</t>
+          <t>15,44; 27,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 12,61</t>
+          <t>0,62; 12,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 31,27</t>
+          <t>-0,02; 9,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,91; 46,51</t>
+          <t>16,62; 45,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,86; 54,28</t>
+          <t>27,79; 55,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 24,06</t>
+          <t>1,05; 23,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 215,3</t>
+          <t>-0,0; 26,91</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,14</t>
+          <t>3,82</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 9,11</t>
+          <t>-2,66; 8,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 15,65</t>
+          <t>4,93; 15,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,59; 21,68</t>
+          <t>9,92; 21,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 7,05</t>
+          <t>-1,18; 8,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 12,36</t>
+          <t>-3,39; 11,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,86; 20,95</t>
+          <t>6,11; 21,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,69; 34,76</t>
+          <t>14,03; 34,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 13,91</t>
+          <t>-2,24; 17,42</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22,8</t>
+          <t>12,11</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,22; 17,61</t>
+          <t>7,08; 18,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 4,59</t>
+          <t>-2,99; 4,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 6,83</t>
+          <t>-2,19; 6,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,34; 37,75</t>
+          <t>6,39; 17,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,64; 23,18</t>
+          <t>8,3; 23,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 4,98</t>
+          <t>-3,12; 4,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 8,02</t>
+          <t>-2,42; 8,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,58; 73,89</t>
+          <t>10,83; 33,86</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,35</t>
+          <t>4,36</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 7,36</t>
+          <t>-1,23; 6,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 5,53</t>
+          <t>-1,07; 5,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 6,74</t>
+          <t>-0,42; 6,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 9,12</t>
+          <t>-0,71; 9,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 8,15</t>
+          <t>-1,27; 7,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 5,97</t>
+          <t>-1,18; 6,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 7,43</t>
+          <t>-0,41; 6,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 13,18</t>
+          <t>-0,69; 14,28</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,8</t>
+          <t>6,69</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,46; 18,0</t>
+          <t>13,23; 18,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,37; 16,16</t>
+          <t>11,17; 16,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,32; 14,0</t>
+          <t>9,02; 13,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,8; 22,19</t>
+          <t>4,48; 9,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,03; 38,58</t>
+          <t>26,86; 38,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,95; 29,61</t>
+          <t>19,68; 29,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,34; 27,43</t>
+          <t>17,1; 27,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,46; 65,97</t>
+          <t>10,97; 24,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación</t>
+          <t>Población que convive con personas con alguna condición, enfermedad crónica o limitación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
